--- a/mds-test/Détails de l’instrument.xlsx
+++ b/mds-test/Détails de l’instrument.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://022gc-my.sharepoint.com/personal/andrew_luong_hc-sc_gc_ca/Documents/Desktop/REP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://022gc-my.sharepoint.com/personal/andrew_luong_hc-sc_gc_ca/Documents/Desktop/Files/REP/Template Updates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{894D3E18-6E1C-4924-B785-1C42E1CCC9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170C761D-1DB2-4FA9-BD0C-3B3C673A653E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F559C21-4AC1-43E1-A9A4-6036973B6A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-16320" windowWidth="16440" windowHeight="28320" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="15" r:id="rId1"/>
@@ -52,8 +52,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={7642E68F-D2DF-46D3-A898-09844B486BC1}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{7642E68F-D2DF-46D3-A898-09844B486BC1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @BLS to confirm FR</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="74">
   <si>
     <t>Veuillez sélectionner les activités réglementaires appropriées menées dans le cadre de la présente demande et compléter la ou les feuilles correspondantes en suivant le ou les liens hypertextes ci-dessous.</t>
   </si>
@@ -460,29 +478,6 @@
     <t>Numéro de l’homologation:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Instructions: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pour les ajouts à une homologation de instruments médicaux existante, remplir le tableau suivant en indiquant le(s) nom(s) de l'instrument, tel(s) qu'il(s) figure(nt) sur l'étiquette de l'instrument, suivi(s) de l'identificateur de l'instrument et de numéro d'identification de l'instrument (le cas échéant) correspondant(s) pour chaque ajout. Développez le tableau et répétez l'opération si nécessaire.</t>
-    </r>
-  </si>
-  <si>
     <t>Nom de l’instrument (conformément à l’étiquette du produit ou la homologation)</t>
   </si>
   <si>
@@ -490,39 +485,6 @@
   </si>
   <si>
     <t>identificateur de l'instrument (code à barres, numéro de modèle ou de pièce)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Instructions:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pour les instruments existants qui doivent être supprimés de l'homologation d'un instrument médicaux, énumérez chaque nom d'instrument ainsi que l'identificateur de l'instrument et le numéro d'identification de l'instrument correspondants. Développez le tableau et répétez l'opération si nécessaire.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Si vous supprimez un identifiant d'appareil complet, veuillez l'indiquer dans la colonne C plutôt que de lister tous les identifiants individuels à supprimer.</t>
-    </r>
   </si>
   <si>
     <t>Nom de l'instrument (tel qu'il figure sur la homologation)</t>
@@ -627,9 +589,6 @@
     <t>Numéro correspondant de l’instrument figurant sur l’homologation du fabricant original</t>
   </si>
   <si>
-    <t>Version 1.0</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -652,12 +611,88 @@
       <t>Un système signifie un instrument medical, y compris un instrument diagnostique in vitro, qui est formé de composants ou parties destinés à être utilisés ensemble pour remplir certaines ou la totalité des fonctions auxquelles il est destiné et qui est vendu sous un seul nom. Les composants du système fabriqués par un autre fabricant doivent faire l'objet d'homologation distincte. Tous les composants d'un système doivent être énumérés dans la demande d'homologation en indiquant le nom et les identifiants des instruments médicaux. La demande doit être accompagnée de la documentation et des renseignements relatifs à tous les composants d'un système.</t>
     </r>
   </si>
+  <si>
+    <t>Numéro de l’homologation d'origine :</t>
+  </si>
+  <si>
+    <t>Numéro de l’homologation de marque privée (si applicable) :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. d'id. de l'instrument (le cas échéant) </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instructions:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pour les ajouts à une homologation de instruments médicaux existante, remplir le tableau suivant en indiquant le(s) nom(s) de l'instrument, tel(s) qu'il(s) figure(nt) sur l'étiquette de l'instrument, suivi(s) de l'identificateur de l'instrument et de numéro d'identification de l'instrument (le cas échéant) correspondant(s) pour chaque ajout. Développez le tableau et répétez l'opération si nécessaire. Si ces ajouts sont de nature non importante et constituent une extension d'un ou de plusieurs identifiants d'instruments déjà figurant sur l'homologation, le type réglementaire correspondant à cette demande doit être « Modification mineure ».</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instructions:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pour les instruments existants qui doivent être supprimés de l'homologation d'un instrument médicaux, énumérez chaque nom d'instrument ainsi que l'identificateur de l'instrument et le numéro d'identification de l'instrument correspondants. Développez le tableau et répétez l'opération si nécessaire. Si vous supprimez un identifiant d'appareil complet, veuillez l'indiquer dans la colonne C plutôt que de lister tous les identifiants individuels à supprimer.</t>
+    </r>
+  </si>
+  <si>
+    <t>Version 1.1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,6 +780,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -760,7 +802,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1252,6 +1294,99 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1259,9 +1394,7 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1366,7 +1499,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1383,11 +1515,100 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1425,50 +1646,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1477,30 +1680,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1584,74 +1763,20 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2827,6 +2952,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Single Device"/>
       <sheetName val="Medical Device Family"/>
@@ -2861,6 +2989,12 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Luong, Andrew (HC/SC)" id="{BE3667B1-EB31-42CC-82C6-B46F51F0B408}" userId="S::andrew.luong@hc-sc.gc.ca::a195a9c2-f308-4621-8eb6-3ebe96fc18dd" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3148,6 +3282,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2026-07-17T19:55:36.70" personId="{BE3667B1-EB31-42CC-82C6-B46F51F0B408}" id="{7642E68F-D2DF-46D3-A898-09844B486BC1}">
+    <text>@BLS to confirm FR</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
@@ -3163,287 +3305,287 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="58"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="90"/>
     </row>
     <row r="3" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="61"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="93"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="55"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
+      <c r="N4" s="87"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="52"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="84"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="49"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="69"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="49"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="69"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="49"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="69"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="49"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="69"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="49"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="69"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="49"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="69"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="81"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="70"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="72"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="71"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="73"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="76"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="78"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="49"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="69"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="49"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="69"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="49"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="69"/>
     </row>
     <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="65"/>
@@ -3461,55 +3603,55 @@
       <c r="N19" s="67"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
+      <c r="B20" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
-      <c r="M20" s="75"/>
-      <c r="N20" s="76"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="78"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="49"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="69"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="49"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="65"/>
@@ -3527,18 +3669,23 @@
       <c r="N23" s="67"/>
     </row>
     <row r="24" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M24" s="119" t="s">
-        <v>69</v>
-      </c>
-      <c r="N24" s="119"/>
+      <c r="M24" s="64" t="s">
+        <v>73</v>
+      </c>
+      <c r="N24" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="B23:N23"/>
-    <mergeCell ref="C18:N18"/>
-    <mergeCell ref="C17:N17"/>
-    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="B5:N5"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B2:N3"/>
+    <mergeCell ref="C10:N10"/>
+    <mergeCell ref="C11:N11"/>
+    <mergeCell ref="C9:N9"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="B12:N12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
     <mergeCell ref="B15:N15"/>
@@ -3546,16 +3693,11 @@
     <mergeCell ref="C22:N22"/>
     <mergeCell ref="B20:N20"/>
     <mergeCell ref="B19:N19"/>
-    <mergeCell ref="C10:N10"/>
-    <mergeCell ref="C11:N11"/>
-    <mergeCell ref="C9:N9"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="B12:N12"/>
-    <mergeCell ref="C7:N7"/>
-    <mergeCell ref="C6:N6"/>
-    <mergeCell ref="B5:N5"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B2:N3"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="B23:N23"/>
+    <mergeCell ref="C18:N18"/>
+    <mergeCell ref="C17:N17"/>
+    <mergeCell ref="C16:N16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" location="'Single Device'!A1" display="Single Device" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -3861,48 +4003,48 @@
         <v>18</v>
       </c>
       <c r="C1" s="34"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>53</v>
       </c>
       <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="102"/>
+      <c r="A2" s="118" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="103"/>
-      <c r="B3" s="104"/>
-      <c r="C3" s="105"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="123"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="103"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="105"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="123"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="106"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="108"/>
+      <c r="A5" s="124"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="126"/>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="129" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="131" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="111" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="113" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="110"/>
-      <c r="B7" s="112"/>
-      <c r="C7" s="114"/>
+      <c r="A7" s="128"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="132"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
@@ -3975,484 +4117,484 @@
       <c r="C21" s="24"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="45"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="45"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="45"/>
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
+      <c r="A41" s="44"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="45"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="45"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="45"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="45"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="45"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="45"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="45"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="45"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="45"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="45"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="45"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
+      <c r="A52" s="44"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="45"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="45"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="45"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="45"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="45"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
+      <c r="A57" s="44"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="45"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
+      <c r="A58" s="44"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="45"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
+      <c r="A59" s="44"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="45"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="45"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
+      <c r="A61" s="44"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="45"/>
-      <c r="B62" s="45"/>
-      <c r="C62" s="45"/>
+      <c r="A62" s="44"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="45"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
+      <c r="A63" s="44"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="45"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
+      <c r="A64" s="44"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="45"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="45"/>
+      <c r="A65" s="44"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="45"/>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="44"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="45"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
+      <c r="A67" s="44"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="45"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
+      <c r="A68" s="44"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="45"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
+      <c r="A69" s="44"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
+      <c r="A70" s="44"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
+      <c r="A71" s="44"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="45"/>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
+      <c r="A72" s="44"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="45"/>
+      <c r="A73" s="44"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="44"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
+      <c r="A74" s="44"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="44"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="45"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
+      <c r="A75" s="44"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="44"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="45"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
+      <c r="A76" s="44"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="45"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
+      <c r="A77" s="44"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="45"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
+      <c r="A78" s="44"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="44"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="45"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
+      <c r="A79" s="44"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="45"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
+      <c r="A80" s="44"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="45"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
+      <c r="A81" s="44"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="44"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="45"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
+      <c r="A82" s="44"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="44"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="45"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
+      <c r="A83" s="44"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="44"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="45"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="45"/>
+      <c r="A84" s="44"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="45"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
+      <c r="A85" s="44"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="45"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="45"/>
+      <c r="A86" s="44"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="45"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
+      <c r="A87" s="44"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="44"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="45"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="45"/>
+      <c r="A88" s="44"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="44"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="45"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
+      <c r="A89" s="44"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="44"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="45"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
+      <c r="A90" s="44"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="45"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
+      <c r="A91" s="44"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="44"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="45"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="45"/>
+      <c r="A92" s="44"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="45"/>
-      <c r="B93" s="45"/>
-      <c r="C93" s="45"/>
+      <c r="A93" s="44"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="44"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="45"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
+      <c r="A94" s="44"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="44"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="45"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
+      <c r="A95" s="44"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="44"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="45"/>
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
+      <c r="A96" s="44"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="44"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="45"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
+      <c r="A97" s="44"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="45"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="45"/>
+      <c r="A98" s="44"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="44"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="45"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
+      <c r="A99" s="44"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
+      <c r="A100" s="44"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="44"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
+      <c r="A101" s="44"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="45"/>
-      <c r="B102" s="45"/>
-      <c r="C102" s="45"/>
+      <c r="A102" s="44"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="45"/>
-      <c r="B103" s="45"/>
-      <c r="C103" s="45"/>
+      <c r="A103" s="44"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="44"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="45"/>
-      <c r="B104" s="45"/>
-      <c r="C104" s="45"/>
+      <c r="A104" s="44"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="44"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="45"/>
-      <c r="B105" s="45"/>
-      <c r="C105" s="45"/>
+      <c r="A105" s="44"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="44"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="45"/>
-      <c r="B106" s="45"/>
-      <c r="C106" s="45"/>
+      <c r="A106" s="44"/>
+      <c r="B106" s="44"/>
+      <c r="C106" s="44"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="45"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="45"/>
+      <c r="A107" s="44"/>
+      <c r="B107" s="44"/>
+      <c r="C107" s="44"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="45"/>
-      <c r="B108" s="45"/>
-      <c r="C108" s="45"/>
+      <c r="A108" s="44"/>
+      <c r="B108" s="44"/>
+      <c r="C108" s="44"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="45"/>
-      <c r="B109" s="45"/>
-      <c r="C109" s="45"/>
+      <c r="A109" s="44"/>
+      <c r="B109" s="44"/>
+      <c r="C109" s="44"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="45"/>
-      <c r="B110" s="45"/>
-      <c r="C110" s="45"/>
+      <c r="A110" s="44"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="44"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="45"/>
-      <c r="B111" s="45"/>
-      <c r="C111" s="45"/>
+      <c r="A111" s="44"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="44"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="45"/>
-      <c r="B112" s="45"/>
-      <c r="C112" s="45"/>
+      <c r="A112" s="44"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="44"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="45"/>
-      <c r="B113" s="45"/>
-      <c r="C113" s="45"/>
+      <c r="A113" s="44"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="44"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="45"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="45"/>
+      <c r="A114" s="44"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="44"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="45"/>
-      <c r="B115" s="45"/>
-      <c r="C115" s="45"/>
+      <c r="A115" s="44"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="45"/>
-      <c r="B116" s="45"/>
-      <c r="C116" s="45"/>
+      <c r="A116" s="44"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="44"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="45"/>
-      <c r="B117" s="45"/>
-      <c r="C117" s="45"/>
+      <c r="A117" s="44"/>
+      <c r="B117" s="44"/>
+      <c r="C117" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4477,157 +4619,157 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:H397"/>
+  <dimension ref="A1:H398"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="17" customWidth="1"/>
     <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="55.28515625" customWidth="1"/>
     <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="7" width="25.7109375" customWidth="1"/>
     <col min="8" max="8" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="133"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="135" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="136"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="49"/>
+      <c r="F2" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="117" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="35"/>
-    </row>
-    <row r="2" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="G2" s="136"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="60"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="61"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="63"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="60"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="60"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="58"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="63"/>
+    </row>
+    <row r="11" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="82"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="84"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="84"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="E11" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="84"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="84"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="84"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="84"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="87"/>
-    </row>
-    <row r="10" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="31" t="s">
+      <c r="F11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="G11" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="H11" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="12"/>
       <c r="D12" s="11"/>
       <c r="E12" s="30"/>
@@ -4758,2627 +4900,2639 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C26" s="44"/>
-      <c r="D26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C27" s="44"/>
+      <c r="C27" s="43"/>
       <c r="D27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="44"/>
+      <c r="C28" s="43"/>
       <c r="D28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="44"/>
+      <c r="C29" s="43"/>
       <c r="D29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="44"/>
+      <c r="C30" s="43"/>
       <c r="D30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C31" s="44"/>
+      <c r="C31" s="43"/>
       <c r="D31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C32" s="44"/>
+      <c r="C32" s="43"/>
       <c r="D32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="44"/>
+      <c r="C33" s="43"/>
       <c r="D33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="44"/>
+      <c r="C34" s="43"/>
       <c r="D34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="44"/>
+      <c r="C35" s="43"/>
       <c r="D35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="44"/>
+      <c r="C36" s="43"/>
       <c r="D36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="44"/>
+      <c r="C37" s="43"/>
       <c r="D37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="44"/>
+      <c r="C38" s="43"/>
       <c r="D38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="44"/>
+      <c r="C39" s="43"/>
       <c r="D39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="44"/>
+      <c r="C40" s="43"/>
       <c r="D40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="44"/>
+      <c r="C41" s="43"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C42" s="44"/>
+      <c r="C42" s="43"/>
       <c r="D42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C43" s="44"/>
+      <c r="C43" s="43"/>
       <c r="D43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C44" s="44"/>
+      <c r="C44" s="43"/>
       <c r="D44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C45" s="44"/>
+      <c r="C45" s="43"/>
       <c r="D45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C46" s="44"/>
+      <c r="C46" s="43"/>
       <c r="D46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C47" s="44"/>
+      <c r="C47" s="43"/>
       <c r="D47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C48" s="44"/>
+      <c r="C48" s="43"/>
       <c r="D48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="44"/>
+      <c r="C49" s="43"/>
       <c r="D49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C50" s="44"/>
+      <c r="C50" s="43"/>
       <c r="D50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="44"/>
+      <c r="C51" s="43"/>
       <c r="D51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C52" s="44"/>
+      <c r="C52" s="43"/>
       <c r="D52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C53" s="44"/>
+      <c r="C53" s="43"/>
       <c r="D53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C54" s="44"/>
+      <c r="C54" s="43"/>
       <c r="D54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C55" s="44"/>
+      <c r="C55" s="43"/>
       <c r="D55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C56" s="44"/>
+      <c r="C56" s="43"/>
       <c r="D56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="44"/>
+      <c r="C57" s="43"/>
       <c r="D57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="44"/>
+      <c r="C58" s="43"/>
       <c r="D58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="44"/>
+      <c r="C59" s="43"/>
       <c r="D59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C60" s="44"/>
+      <c r="C60" s="43"/>
       <c r="D60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="44"/>
+      <c r="C61" s="43"/>
       <c r="D61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C62" s="44"/>
+      <c r="C62" s="43"/>
       <c r="D62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C63" s="44"/>
+      <c r="C63" s="43"/>
       <c r="D63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C64" s="44"/>
+      <c r="C64" s="43"/>
       <c r="D64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C65" s="44"/>
+      <c r="C65" s="43"/>
       <c r="D65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C66" s="44"/>
+      <c r="C66" s="43"/>
       <c r="D66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C67" s="44"/>
+      <c r="C67" s="43"/>
       <c r="D67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C68" s="44"/>
+      <c r="C68" s="43"/>
       <c r="D68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C69" s="44"/>
+      <c r="C69" s="43"/>
       <c r="D69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C70" s="44"/>
+      <c r="C70" s="43"/>
       <c r="D70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C71" s="44"/>
+      <c r="C71" s="43"/>
       <c r="D71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C72" s="44"/>
+      <c r="C72" s="43"/>
       <c r="D72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C73" s="44"/>
+      <c r="C73" s="43"/>
       <c r="D73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C74" s="44"/>
+      <c r="C74" s="43"/>
       <c r="D74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C75" s="44"/>
+      <c r="C75" s="43"/>
       <c r="D75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C76" s="44"/>
+      <c r="C76" s="43"/>
       <c r="D76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C77" s="44"/>
+      <c r="C77" s="43"/>
       <c r="D77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C78" s="44"/>
+      <c r="C78" s="43"/>
       <c r="D78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C79" s="44"/>
+      <c r="C79" s="43"/>
       <c r="D79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C80" s="44"/>
+      <c r="C80" s="43"/>
       <c r="D80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C81" s="44"/>
+      <c r="C81" s="43"/>
       <c r="D81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C82" s="44"/>
+      <c r="C82" s="43"/>
       <c r="D82" s="6"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C83" s="44"/>
+      <c r="C83" s="43"/>
       <c r="D83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C84" s="44"/>
+      <c r="C84" s="43"/>
       <c r="D84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
     </row>
     <row r="85" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C85" s="44"/>
+      <c r="C85" s="43"/>
       <c r="D85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
     </row>
     <row r="86" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="44"/>
+      <c r="C86" s="43"/>
       <c r="D86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C87" s="44"/>
+      <c r="C87" s="43"/>
       <c r="D87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
     </row>
     <row r="88" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C88" s="44"/>
+      <c r="C88" s="43"/>
       <c r="D88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
     </row>
     <row r="89" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C89" s="44"/>
+      <c r="C89" s="43"/>
       <c r="D89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
     </row>
     <row r="90" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C90" s="44"/>
+      <c r="C90" s="43"/>
       <c r="D90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
     </row>
     <row r="91" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C91" s="44"/>
+      <c r="C91" s="43"/>
       <c r="D91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C92" s="44"/>
+      <c r="C92" s="43"/>
       <c r="D92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C93" s="44"/>
+      <c r="C93" s="43"/>
       <c r="D93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C94" s="44"/>
+      <c r="C94" s="43"/>
       <c r="D94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C95" s="44"/>
+      <c r="C95" s="43"/>
       <c r="D95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C96" s="44"/>
+      <c r="C96" s="43"/>
       <c r="D96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
     </row>
     <row r="97" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C97" s="44"/>
+      <c r="C97" s="43"/>
       <c r="D97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C98" s="44"/>
+      <c r="C98" s="43"/>
       <c r="D98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C99" s="44"/>
+      <c r="C99" s="43"/>
       <c r="D99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C100" s="44"/>
+      <c r="C100" s="43"/>
       <c r="D100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C101" s="44"/>
+      <c r="C101" s="43"/>
       <c r="D101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
     </row>
     <row r="102" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C102" s="44"/>
+      <c r="C102" s="43"/>
       <c r="D102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
     </row>
     <row r="103" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C103" s="44"/>
+      <c r="C103" s="43"/>
       <c r="D103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
     </row>
     <row r="104" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C104" s="44"/>
+      <c r="C104" s="43"/>
       <c r="D104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
     </row>
     <row r="105" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C105" s="44"/>
+      <c r="C105" s="43"/>
       <c r="D105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
     </row>
     <row r="106" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C106" s="44"/>
+      <c r="C106" s="43"/>
       <c r="D106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
     </row>
     <row r="107" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C107" s="44"/>
+      <c r="C107" s="43"/>
       <c r="D107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
     </row>
     <row r="108" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C108" s="44"/>
+      <c r="C108" s="43"/>
       <c r="D108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
     </row>
     <row r="109" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C109" s="44"/>
+      <c r="C109" s="43"/>
       <c r="D109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
     </row>
     <row r="110" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C110" s="44"/>
+      <c r="C110" s="43"/>
       <c r="D110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
     </row>
     <row r="111" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C111" s="44"/>
+      <c r="C111" s="43"/>
       <c r="D111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
     </row>
     <row r="112" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C112" s="44"/>
+      <c r="C112" s="43"/>
       <c r="D112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
     </row>
     <row r="113" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C113" s="44"/>
+      <c r="C113" s="43"/>
       <c r="D113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
     </row>
     <row r="114" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C114" s="44"/>
+      <c r="C114" s="43"/>
       <c r="D114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
     </row>
     <row r="115" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C115" s="44"/>
+      <c r="C115" s="43"/>
       <c r="D115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
     </row>
     <row r="116" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C116" s="44"/>
+      <c r="C116" s="43"/>
       <c r="D116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
     </row>
     <row r="117" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C117" s="44"/>
+      <c r="C117" s="43"/>
       <c r="D117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
     </row>
     <row r="118" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C118" s="44"/>
+      <c r="C118" s="43"/>
       <c r="D118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
     </row>
     <row r="119" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C119" s="44"/>
+      <c r="C119" s="43"/>
       <c r="D119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
     </row>
     <row r="120" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C120" s="44"/>
+      <c r="C120" s="43"/>
       <c r="D120" s="6"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
     </row>
     <row r="121" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C121" s="44"/>
+      <c r="C121" s="43"/>
       <c r="D121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
     </row>
     <row r="122" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C122" s="44"/>
+      <c r="C122" s="43"/>
       <c r="D122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
     </row>
     <row r="123" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C123" s="44"/>
+      <c r="C123" s="43"/>
       <c r="D123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
     </row>
     <row r="124" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C124" s="44"/>
+      <c r="C124" s="43"/>
       <c r="D124" s="6"/>
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
     </row>
     <row r="125" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C125" s="44"/>
+      <c r="C125" s="43"/>
       <c r="D125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
     </row>
     <row r="126" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C126" s="44"/>
+      <c r="C126" s="43"/>
       <c r="D126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
     </row>
     <row r="127" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C127" s="44"/>
+      <c r="C127" s="43"/>
       <c r="D127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
     </row>
     <row r="128" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C128" s="44"/>
+      <c r="C128" s="43"/>
       <c r="D128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
     </row>
     <row r="129" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C129" s="44"/>
+      <c r="C129" s="43"/>
       <c r="D129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
     </row>
     <row r="130" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C130" s="44"/>
+      <c r="C130" s="43"/>
       <c r="D130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
     </row>
     <row r="131" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C131" s="44"/>
+      <c r="C131" s="43"/>
       <c r="D131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C132" s="44"/>
+      <c r="C132" s="43"/>
       <c r="D132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
     </row>
     <row r="133" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C133" s="44"/>
+      <c r="C133" s="43"/>
       <c r="D133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
     </row>
     <row r="134" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C134" s="44"/>
+      <c r="C134" s="43"/>
       <c r="D134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
     </row>
     <row r="135" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C135" s="44"/>
+      <c r="C135" s="43"/>
       <c r="D135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
     </row>
     <row r="136" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C136" s="44"/>
+      <c r="C136" s="43"/>
       <c r="D136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
     </row>
     <row r="137" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C137" s="44"/>
+      <c r="C137" s="43"/>
       <c r="D137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
     </row>
     <row r="138" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C138" s="44"/>
+      <c r="C138" s="43"/>
       <c r="D138" s="6"/>
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
     </row>
     <row r="139" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C139" s="44"/>
+      <c r="C139" s="43"/>
       <c r="D139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
     </row>
     <row r="140" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C140" s="44"/>
+      <c r="C140" s="43"/>
       <c r="D140" s="6"/>
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
     </row>
     <row r="141" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C141" s="44"/>
+      <c r="C141" s="43"/>
       <c r="D141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
     </row>
     <row r="142" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C142" s="44"/>
+      <c r="C142" s="43"/>
       <c r="D142" s="6"/>
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
     </row>
     <row r="143" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C143" s="44"/>
+      <c r="C143" s="43"/>
       <c r="D143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
     </row>
     <row r="144" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C144" s="44"/>
+      <c r="C144" s="43"/>
       <c r="D144" s="6"/>
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
     </row>
     <row r="145" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C145" s="44"/>
+      <c r="C145" s="43"/>
       <c r="D145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
     </row>
     <row r="146" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C146" s="44"/>
+      <c r="C146" s="43"/>
       <c r="D146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
     </row>
     <row r="147" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C147" s="44"/>
+      <c r="C147" s="43"/>
       <c r="D147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
     </row>
     <row r="148" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C148" s="44"/>
+      <c r="C148" s="43"/>
       <c r="D148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
     </row>
     <row r="149" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C149" s="44"/>
+      <c r="C149" s="43"/>
       <c r="D149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
     </row>
     <row r="150" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C150" s="44"/>
+      <c r="C150" s="43"/>
       <c r="D150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
     </row>
     <row r="151" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C151" s="44"/>
+      <c r="C151" s="43"/>
       <c r="D151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
     </row>
     <row r="152" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C152" s="44"/>
+      <c r="C152" s="43"/>
       <c r="D152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
     </row>
     <row r="153" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C153" s="44"/>
+      <c r="C153" s="43"/>
       <c r="D153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
     </row>
     <row r="154" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C154" s="44"/>
+      <c r="C154" s="43"/>
       <c r="D154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
     </row>
     <row r="155" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C155" s="44"/>
+      <c r="C155" s="43"/>
       <c r="D155" s="6"/>
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
     </row>
     <row r="156" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C156" s="44"/>
+      <c r="C156" s="43"/>
       <c r="D156" s="6"/>
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
     </row>
     <row r="157" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C157" s="44"/>
+      <c r="C157" s="43"/>
       <c r="D157" s="6"/>
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
     </row>
     <row r="158" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C158" s="44"/>
+      <c r="C158" s="43"/>
       <c r="D158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
     </row>
     <row r="159" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C159" s="44"/>
+      <c r="C159" s="43"/>
       <c r="D159" s="6"/>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
     </row>
     <row r="160" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C160" s="44"/>
+      <c r="C160" s="43"/>
       <c r="D160" s="6"/>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
     </row>
     <row r="161" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C161" s="44"/>
+      <c r="C161" s="43"/>
       <c r="D161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
     </row>
     <row r="162" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C162" s="44"/>
+      <c r="C162" s="43"/>
       <c r="D162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
     </row>
     <row r="163" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C163" s="44"/>
+      <c r="C163" s="43"/>
       <c r="D163" s="6"/>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
     </row>
     <row r="164" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C164" s="44"/>
+      <c r="C164" s="43"/>
       <c r="D164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
     </row>
     <row r="165" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C165" s="44"/>
+      <c r="C165" s="43"/>
       <c r="D165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
     </row>
     <row r="166" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C166" s="44"/>
+      <c r="C166" s="43"/>
       <c r="D166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
     </row>
     <row r="167" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C167" s="44"/>
+      <c r="C167" s="43"/>
       <c r="D167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
     </row>
     <row r="168" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C168" s="44"/>
+      <c r="C168" s="43"/>
       <c r="D168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
     </row>
     <row r="169" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C169" s="44"/>
+      <c r="C169" s="43"/>
       <c r="D169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
     </row>
     <row r="170" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C170" s="44"/>
+      <c r="C170" s="43"/>
       <c r="D170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
     </row>
     <row r="171" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C171" s="44"/>
+      <c r="C171" s="43"/>
       <c r="D171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
     </row>
     <row r="172" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C172" s="44"/>
+      <c r="C172" s="43"/>
       <c r="D172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
     </row>
     <row r="173" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C173" s="44"/>
+      <c r="C173" s="43"/>
       <c r="D173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
     </row>
     <row r="174" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C174" s="44"/>
+      <c r="C174" s="43"/>
       <c r="D174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
     </row>
     <row r="175" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C175" s="44"/>
+      <c r="C175" s="43"/>
       <c r="D175" s="6"/>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
     </row>
     <row r="176" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C176" s="44"/>
+      <c r="C176" s="43"/>
       <c r="D176" s="6"/>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
     </row>
     <row r="177" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C177" s="44"/>
+      <c r="C177" s="43"/>
       <c r="D177" s="6"/>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
     </row>
     <row r="178" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C178" s="44"/>
+      <c r="C178" s="43"/>
       <c r="D178" s="6"/>
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
     </row>
     <row r="179" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C179" s="44"/>
+      <c r="C179" s="43"/>
       <c r="D179" s="6"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
     </row>
     <row r="180" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C180" s="44"/>
+      <c r="C180" s="43"/>
       <c r="D180" s="6"/>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
     </row>
     <row r="181" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C181" s="44"/>
+      <c r="C181" s="43"/>
       <c r="D181" s="6"/>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
     </row>
     <row r="182" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C182" s="44"/>
+      <c r="C182" s="43"/>
       <c r="D182" s="6"/>
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
     </row>
     <row r="183" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C183" s="44"/>
+      <c r="C183" s="43"/>
       <c r="D183" s="6"/>
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
     </row>
     <row r="184" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C184" s="44"/>
+      <c r="C184" s="43"/>
       <c r="D184" s="6"/>
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
     </row>
     <row r="185" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C185" s="44"/>
+      <c r="C185" s="43"/>
       <c r="D185" s="6"/>
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
     </row>
     <row r="186" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C186" s="44"/>
+      <c r="C186" s="43"/>
       <c r="D186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
     </row>
     <row r="187" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C187" s="44"/>
+      <c r="C187" s="43"/>
       <c r="D187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
     </row>
     <row r="188" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C188" s="44"/>
+      <c r="C188" s="43"/>
       <c r="D188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
     </row>
     <row r="189" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C189" s="44"/>
+      <c r="C189" s="43"/>
       <c r="D189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
     </row>
     <row r="190" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C190" s="44"/>
+      <c r="C190" s="43"/>
       <c r="D190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
     </row>
     <row r="191" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C191" s="44"/>
+      <c r="C191" s="43"/>
       <c r="D191" s="6"/>
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
     </row>
     <row r="192" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C192" s="44"/>
+      <c r="C192" s="43"/>
       <c r="D192" s="6"/>
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
     </row>
     <row r="193" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C193" s="44"/>
+      <c r="C193" s="43"/>
       <c r="D193" s="6"/>
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
     </row>
     <row r="194" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C194" s="44"/>
+      <c r="C194" s="43"/>
       <c r="D194" s="6"/>
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
     </row>
     <row r="195" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C195" s="44"/>
+      <c r="C195" s="43"/>
       <c r="D195" s="6"/>
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
     </row>
     <row r="196" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C196" s="44"/>
+      <c r="C196" s="43"/>
       <c r="D196" s="6"/>
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
     </row>
     <row r="197" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C197" s="44"/>
+      <c r="C197" s="43"/>
       <c r="D197" s="6"/>
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
     </row>
     <row r="198" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C198" s="44"/>
+      <c r="C198" s="43"/>
       <c r="D198" s="6"/>
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
     </row>
     <row r="199" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C199" s="44"/>
+      <c r="C199" s="43"/>
       <c r="D199" s="6"/>
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
     </row>
     <row r="200" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C200" s="44"/>
+      <c r="C200" s="43"/>
       <c r="D200" s="6"/>
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
     </row>
     <row r="201" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C201" s="44"/>
+      <c r="C201" s="43"/>
       <c r="D201" s="6"/>
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
     </row>
     <row r="202" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C202" s="44"/>
+      <c r="C202" s="43"/>
       <c r="D202" s="6"/>
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
     </row>
     <row r="203" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C203" s="44"/>
+      <c r="C203" s="43"/>
       <c r="D203" s="6"/>
       <c r="F203" s="6"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
     </row>
     <row r="204" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C204" s="44"/>
+      <c r="C204" s="43"/>
       <c r="D204" s="6"/>
       <c r="F204" s="6"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
     </row>
     <row r="205" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C205" s="44"/>
+      <c r="C205" s="43"/>
       <c r="D205" s="6"/>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
     </row>
     <row r="206" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C206" s="44"/>
+      <c r="C206" s="43"/>
       <c r="D206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
     </row>
     <row r="207" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C207" s="44"/>
+      <c r="C207" s="43"/>
       <c r="D207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
     </row>
     <row r="208" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C208" s="44"/>
+      <c r="C208" s="43"/>
       <c r="D208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
     </row>
     <row r="209" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C209" s="44"/>
+      <c r="C209" s="43"/>
       <c r="D209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
     </row>
     <row r="210" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C210" s="44"/>
+      <c r="C210" s="43"/>
       <c r="D210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
     </row>
     <row r="211" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C211" s="44"/>
+      <c r="C211" s="43"/>
       <c r="D211" s="6"/>
       <c r="F211" s="6"/>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
     </row>
     <row r="212" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C212" s="44"/>
+      <c r="C212" s="43"/>
       <c r="D212" s="6"/>
       <c r="F212" s="6"/>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
     </row>
     <row r="213" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C213" s="44"/>
+      <c r="C213" s="43"/>
       <c r="D213" s="6"/>
       <c r="F213" s="6"/>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
     </row>
     <row r="214" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C214" s="44"/>
+      <c r="C214" s="43"/>
       <c r="D214" s="6"/>
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
     </row>
     <row r="215" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C215" s="44"/>
+      <c r="C215" s="43"/>
       <c r="D215" s="6"/>
       <c r="F215" s="6"/>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
     </row>
     <row r="216" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C216" s="44"/>
+      <c r="C216" s="43"/>
       <c r="D216" s="6"/>
       <c r="F216" s="6"/>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
     </row>
     <row r="217" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C217" s="44"/>
+      <c r="C217" s="43"/>
       <c r="D217" s="6"/>
       <c r="F217" s="6"/>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
     </row>
     <row r="218" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C218" s="44"/>
+      <c r="C218" s="43"/>
       <c r="D218" s="6"/>
       <c r="F218" s="6"/>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
     </row>
     <row r="219" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C219" s="44"/>
+      <c r="C219" s="43"/>
       <c r="D219" s="6"/>
       <c r="F219" s="6"/>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
     </row>
     <row r="220" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C220" s="44"/>
+      <c r="C220" s="43"/>
       <c r="D220" s="6"/>
       <c r="F220" s="6"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
     </row>
     <row r="221" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C221" s="44"/>
+      <c r="C221" s="43"/>
       <c r="D221" s="6"/>
       <c r="F221" s="6"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
     </row>
     <row r="222" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C222" s="44"/>
+      <c r="C222" s="43"/>
       <c r="D222" s="6"/>
       <c r="F222" s="6"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
     </row>
     <row r="223" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C223" s="44"/>
+      <c r="C223" s="43"/>
       <c r="D223" s="6"/>
       <c r="F223" s="6"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
     </row>
     <row r="224" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C224" s="44"/>
+      <c r="C224" s="43"/>
       <c r="D224" s="6"/>
       <c r="F224" s="6"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
     </row>
     <row r="225" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C225" s="44"/>
+      <c r="C225" s="43"/>
       <c r="D225" s="6"/>
       <c r="F225" s="6"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
     </row>
     <row r="226" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C226" s="44"/>
+      <c r="C226" s="43"/>
       <c r="D226" s="6"/>
       <c r="F226" s="6"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
     </row>
     <row r="227" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C227" s="44"/>
+      <c r="C227" s="43"/>
       <c r="D227" s="6"/>
       <c r="F227" s="6"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
     </row>
     <row r="228" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C228" s="44"/>
+      <c r="C228" s="43"/>
       <c r="D228" s="6"/>
       <c r="F228" s="6"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
     </row>
     <row r="229" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C229" s="44"/>
+      <c r="C229" s="43"/>
       <c r="D229" s="6"/>
       <c r="F229" s="6"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
     </row>
     <row r="230" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C230" s="44"/>
+      <c r="C230" s="43"/>
       <c r="D230" s="6"/>
       <c r="F230" s="6"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
     </row>
     <row r="231" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C231" s="44"/>
+      <c r="C231" s="43"/>
       <c r="D231" s="6"/>
       <c r="F231" s="6"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
     </row>
     <row r="232" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C232" s="44"/>
+      <c r="C232" s="43"/>
       <c r="D232" s="6"/>
       <c r="F232" s="6"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
     </row>
     <row r="233" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C233" s="44"/>
+      <c r="C233" s="43"/>
       <c r="D233" s="6"/>
       <c r="F233" s="6"/>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
     </row>
     <row r="234" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C234" s="44"/>
+      <c r="C234" s="43"/>
       <c r="D234" s="6"/>
       <c r="F234" s="6"/>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
     </row>
     <row r="235" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C235" s="44"/>
+      <c r="C235" s="43"/>
       <c r="D235" s="6"/>
       <c r="F235" s="6"/>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
     </row>
     <row r="236" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C236" s="44"/>
+      <c r="C236" s="43"/>
       <c r="D236" s="6"/>
       <c r="F236" s="6"/>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
     </row>
     <row r="237" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C237" s="44"/>
+      <c r="C237" s="43"/>
       <c r="D237" s="6"/>
       <c r="F237" s="6"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
     </row>
     <row r="238" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C238" s="44"/>
+      <c r="C238" s="43"/>
       <c r="D238" s="6"/>
       <c r="F238" s="6"/>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
     </row>
     <row r="239" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C239" s="44"/>
+      <c r="C239" s="43"/>
       <c r="D239" s="6"/>
       <c r="F239" s="6"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
     </row>
     <row r="240" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C240" s="44"/>
+      <c r="C240" s="43"/>
       <c r="D240" s="6"/>
       <c r="F240" s="6"/>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
     </row>
     <row r="241" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C241" s="44"/>
+      <c r="C241" s="43"/>
       <c r="D241" s="6"/>
       <c r="F241" s="6"/>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
     </row>
     <row r="242" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C242" s="44"/>
+      <c r="C242" s="43"/>
       <c r="D242" s="6"/>
       <c r="F242" s="6"/>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
     </row>
     <row r="243" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C243" s="44"/>
+      <c r="C243" s="43"/>
       <c r="D243" s="6"/>
       <c r="F243" s="6"/>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
     </row>
     <row r="244" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C244" s="44"/>
+      <c r="C244" s="43"/>
       <c r="D244" s="6"/>
       <c r="F244" s="6"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
     </row>
     <row r="245" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C245" s="44"/>
+      <c r="C245" s="43"/>
       <c r="D245" s="6"/>
       <c r="F245" s="6"/>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
     </row>
     <row r="246" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C246" s="44"/>
+      <c r="C246" s="43"/>
       <c r="D246" s="6"/>
       <c r="F246" s="6"/>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
     </row>
     <row r="247" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C247" s="44"/>
+      <c r="C247" s="43"/>
       <c r="D247" s="6"/>
       <c r="F247" s="6"/>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
     </row>
     <row r="248" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C248" s="44"/>
+      <c r="C248" s="43"/>
       <c r="D248" s="6"/>
       <c r="F248" s="6"/>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
     </row>
     <row r="249" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C249" s="44"/>
+      <c r="C249" s="43"/>
       <c r="D249" s="6"/>
       <c r="F249" s="6"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
     </row>
     <row r="250" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C250" s="44"/>
+      <c r="C250" s="43"/>
       <c r="D250" s="6"/>
       <c r="F250" s="6"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
     </row>
     <row r="251" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C251" s="44"/>
+      <c r="C251" s="43"/>
       <c r="D251" s="6"/>
       <c r="F251" s="6"/>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
     </row>
     <row r="252" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C252" s="44"/>
+      <c r="C252" s="43"/>
       <c r="D252" s="6"/>
       <c r="F252" s="6"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
     </row>
     <row r="253" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C253" s="44"/>
+      <c r="C253" s="43"/>
       <c r="D253" s="6"/>
       <c r="F253" s="6"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
     </row>
     <row r="254" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C254" s="44"/>
+      <c r="C254" s="43"/>
       <c r="D254" s="6"/>
       <c r="F254" s="6"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
     </row>
     <row r="255" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C255" s="44"/>
+      <c r="C255" s="43"/>
       <c r="D255" s="6"/>
       <c r="F255" s="6"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
     </row>
     <row r="256" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C256" s="44"/>
+      <c r="C256" s="43"/>
       <c r="D256" s="6"/>
       <c r="F256" s="6"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
     </row>
     <row r="257" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C257" s="44"/>
+      <c r="C257" s="43"/>
       <c r="D257" s="6"/>
       <c r="F257" s="6"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
     </row>
     <row r="258" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C258" s="44"/>
+      <c r="C258" s="43"/>
       <c r="D258" s="6"/>
       <c r="F258" s="6"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
     </row>
     <row r="259" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C259" s="44"/>
+      <c r="C259" s="43"/>
       <c r="D259" s="6"/>
       <c r="F259" s="6"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
     </row>
     <row r="260" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C260" s="44"/>
+      <c r="C260" s="43"/>
       <c r="D260" s="6"/>
       <c r="F260" s="6"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
     </row>
     <row r="261" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C261" s="44"/>
+      <c r="C261" s="43"/>
       <c r="D261" s="6"/>
       <c r="F261" s="6"/>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
     </row>
     <row r="262" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C262" s="44"/>
+      <c r="C262" s="43"/>
       <c r="D262" s="6"/>
       <c r="F262" s="6"/>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
     </row>
     <row r="263" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C263" s="44"/>
+      <c r="C263" s="43"/>
       <c r="D263" s="6"/>
       <c r="F263" s="6"/>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
     </row>
     <row r="264" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C264" s="44"/>
+      <c r="C264" s="43"/>
       <c r="D264" s="6"/>
       <c r="F264" s="6"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
     </row>
     <row r="265" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C265" s="44"/>
+      <c r="C265" s="43"/>
       <c r="D265" s="6"/>
       <c r="F265" s="6"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
     </row>
     <row r="266" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C266" s="44"/>
+      <c r="C266" s="43"/>
       <c r="D266" s="6"/>
       <c r="F266" s="6"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
     </row>
     <row r="267" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C267" s="44"/>
+      <c r="C267" s="43"/>
       <c r="D267" s="6"/>
       <c r="F267" s="6"/>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
     </row>
     <row r="268" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C268" s="44"/>
+      <c r="C268" s="43"/>
       <c r="D268" s="6"/>
       <c r="F268" s="6"/>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
     </row>
     <row r="269" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C269" s="44"/>
+      <c r="C269" s="43"/>
       <c r="D269" s="6"/>
       <c r="F269" s="6"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
     </row>
     <row r="270" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C270" s="44"/>
+      <c r="C270" s="43"/>
       <c r="D270" s="6"/>
       <c r="F270" s="6"/>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
     </row>
     <row r="271" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C271" s="44"/>
+      <c r="C271" s="43"/>
       <c r="D271" s="6"/>
       <c r="F271" s="6"/>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
     </row>
     <row r="272" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C272" s="44"/>
+      <c r="C272" s="43"/>
       <c r="D272" s="6"/>
       <c r="F272" s="6"/>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
     </row>
     <row r="273" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C273" s="44"/>
+      <c r="C273" s="43"/>
       <c r="D273" s="6"/>
       <c r="F273" s="6"/>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
     </row>
     <row r="274" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C274" s="44"/>
+      <c r="C274" s="43"/>
       <c r="D274" s="6"/>
       <c r="F274" s="6"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
     </row>
     <row r="275" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C275" s="44"/>
+      <c r="C275" s="43"/>
       <c r="D275" s="6"/>
       <c r="F275" s="6"/>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
     </row>
     <row r="276" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C276" s="44"/>
+      <c r="C276" s="43"/>
       <c r="D276" s="6"/>
       <c r="F276" s="6"/>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
     </row>
     <row r="277" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C277" s="44"/>
+      <c r="C277" s="43"/>
       <c r="D277" s="6"/>
       <c r="F277" s="6"/>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
     </row>
     <row r="278" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C278" s="44"/>
+      <c r="C278" s="43"/>
       <c r="D278" s="6"/>
       <c r="F278" s="6"/>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
     </row>
     <row r="279" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C279" s="44"/>
+      <c r="C279" s="43"/>
       <c r="D279" s="6"/>
       <c r="F279" s="6"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
     </row>
     <row r="280" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C280" s="44"/>
+      <c r="C280" s="43"/>
       <c r="D280" s="6"/>
       <c r="F280" s="6"/>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
     </row>
     <row r="281" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C281" s="44"/>
+      <c r="C281" s="43"/>
       <c r="D281" s="6"/>
       <c r="F281" s="6"/>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
     </row>
     <row r="282" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C282" s="44"/>
+      <c r="C282" s="43"/>
       <c r="D282" s="6"/>
       <c r="F282" s="6"/>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
     </row>
     <row r="283" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C283" s="44"/>
+      <c r="C283" s="43"/>
       <c r="D283" s="6"/>
       <c r="F283" s="6"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
     </row>
     <row r="284" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C284" s="44"/>
+      <c r="C284" s="43"/>
       <c r="D284" s="6"/>
       <c r="F284" s="6"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
     </row>
     <row r="285" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C285" s="44"/>
+      <c r="C285" s="43"/>
       <c r="D285" s="6"/>
       <c r="F285" s="6"/>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
     </row>
     <row r="286" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C286" s="44"/>
+      <c r="C286" s="43"/>
       <c r="D286" s="6"/>
       <c r="F286" s="6"/>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
     </row>
     <row r="287" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C287" s="44"/>
+      <c r="C287" s="43"/>
       <c r="D287" s="6"/>
       <c r="F287" s="6"/>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
     </row>
     <row r="288" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C288" s="44"/>
+      <c r="C288" s="43"/>
       <c r="D288" s="6"/>
       <c r="F288" s="6"/>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
     </row>
     <row r="289" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C289" s="44"/>
+      <c r="C289" s="43"/>
       <c r="D289" s="6"/>
       <c r="F289" s="6"/>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
     </row>
     <row r="290" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C290" s="44"/>
+      <c r="C290" s="43"/>
       <c r="D290" s="6"/>
       <c r="F290" s="6"/>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
     </row>
     <row r="291" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C291" s="44"/>
+      <c r="C291" s="43"/>
       <c r="D291" s="6"/>
       <c r="F291" s="6"/>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
     </row>
     <row r="292" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C292" s="44"/>
+      <c r="C292" s="43"/>
       <c r="D292" s="6"/>
       <c r="F292" s="6"/>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
     </row>
     <row r="293" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C293" s="44"/>
+      <c r="C293" s="43"/>
       <c r="D293" s="6"/>
       <c r="F293" s="6"/>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
     </row>
     <row r="294" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C294" s="44"/>
+      <c r="C294" s="43"/>
       <c r="D294" s="6"/>
       <c r="F294" s="6"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
     </row>
     <row r="295" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C295" s="44"/>
+      <c r="C295" s="43"/>
       <c r="D295" s="6"/>
       <c r="F295" s="6"/>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
     </row>
     <row r="296" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C296" s="44"/>
+      <c r="C296" s="43"/>
       <c r="D296" s="6"/>
       <c r="F296" s="6"/>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
     </row>
     <row r="297" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C297" s="44"/>
+      <c r="C297" s="43"/>
       <c r="D297" s="6"/>
       <c r="F297" s="6"/>
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
     </row>
     <row r="298" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C298" s="44"/>
+      <c r="C298" s="43"/>
       <c r="D298" s="6"/>
       <c r="F298" s="6"/>
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
     </row>
     <row r="299" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C299" s="44"/>
+      <c r="C299" s="43"/>
       <c r="D299" s="6"/>
       <c r="F299" s="6"/>
       <c r="G299" s="6"/>
       <c r="H299" s="6"/>
     </row>
     <row r="300" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C300" s="44"/>
+      <c r="C300" s="43"/>
       <c r="D300" s="6"/>
       <c r="F300" s="6"/>
       <c r="G300" s="6"/>
       <c r="H300" s="6"/>
     </row>
     <row r="301" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C301" s="44"/>
+      <c r="C301" s="43"/>
       <c r="D301" s="6"/>
       <c r="F301" s="6"/>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
     </row>
     <row r="302" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C302" s="44"/>
+      <c r="C302" s="43"/>
       <c r="D302" s="6"/>
       <c r="F302" s="6"/>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
     </row>
     <row r="303" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C303" s="44"/>
+      <c r="C303" s="43"/>
       <c r="D303" s="6"/>
       <c r="F303" s="6"/>
       <c r="G303" s="6"/>
       <c r="H303" s="6"/>
     </row>
     <row r="304" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C304" s="44"/>
+      <c r="C304" s="43"/>
       <c r="D304" s="6"/>
       <c r="F304" s="6"/>
       <c r="G304" s="6"/>
       <c r="H304" s="6"/>
     </row>
     <row r="305" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C305" s="44"/>
+      <c r="C305" s="43"/>
       <c r="D305" s="6"/>
       <c r="F305" s="6"/>
       <c r="G305" s="6"/>
       <c r="H305" s="6"/>
     </row>
     <row r="306" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C306" s="44"/>
+      <c r="C306" s="43"/>
       <c r="D306" s="6"/>
       <c r="F306" s="6"/>
       <c r="G306" s="6"/>
       <c r="H306" s="6"/>
     </row>
     <row r="307" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C307" s="44"/>
+      <c r="C307" s="43"/>
       <c r="D307" s="6"/>
       <c r="F307" s="6"/>
       <c r="G307" s="6"/>
       <c r="H307" s="6"/>
     </row>
     <row r="308" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C308" s="44"/>
+      <c r="C308" s="43"/>
       <c r="D308" s="6"/>
       <c r="F308" s="6"/>
       <c r="G308" s="6"/>
       <c r="H308" s="6"/>
     </row>
     <row r="309" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C309" s="44"/>
+      <c r="C309" s="43"/>
       <c r="D309" s="6"/>
       <c r="F309" s="6"/>
       <c r="G309" s="6"/>
       <c r="H309" s="6"/>
     </row>
     <row r="310" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C310" s="44"/>
+      <c r="C310" s="43"/>
       <c r="D310" s="6"/>
       <c r="F310" s="6"/>
       <c r="G310" s="6"/>
       <c r="H310" s="6"/>
     </row>
     <row r="311" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C311" s="44"/>
+      <c r="C311" s="43"/>
       <c r="D311" s="6"/>
       <c r="F311" s="6"/>
       <c r="G311" s="6"/>
       <c r="H311" s="6"/>
     </row>
     <row r="312" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C312" s="44"/>
+      <c r="C312" s="43"/>
       <c r="D312" s="6"/>
       <c r="F312" s="6"/>
       <c r="G312" s="6"/>
       <c r="H312" s="6"/>
     </row>
     <row r="313" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C313" s="44"/>
+      <c r="C313" s="43"/>
       <c r="D313" s="6"/>
       <c r="F313" s="6"/>
       <c r="G313" s="6"/>
       <c r="H313" s="6"/>
     </row>
     <row r="314" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C314" s="44"/>
+      <c r="C314" s="43"/>
       <c r="D314" s="6"/>
       <c r="F314" s="6"/>
       <c r="G314" s="6"/>
       <c r="H314" s="6"/>
     </row>
     <row r="315" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C315" s="44"/>
+      <c r="C315" s="43"/>
       <c r="D315" s="6"/>
       <c r="F315" s="6"/>
       <c r="G315" s="6"/>
       <c r="H315" s="6"/>
     </row>
     <row r="316" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C316" s="44"/>
+      <c r="C316" s="43"/>
       <c r="D316" s="6"/>
       <c r="F316" s="6"/>
       <c r="G316" s="6"/>
       <c r="H316" s="6"/>
     </row>
     <row r="317" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C317" s="44"/>
+      <c r="C317" s="43"/>
       <c r="D317" s="6"/>
       <c r="F317" s="6"/>
       <c r="G317" s="6"/>
       <c r="H317" s="6"/>
     </row>
     <row r="318" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C318" s="44"/>
+      <c r="C318" s="43"/>
       <c r="D318" s="6"/>
       <c r="F318" s="6"/>
       <c r="G318" s="6"/>
       <c r="H318" s="6"/>
     </row>
     <row r="319" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C319" s="44"/>
+      <c r="C319" s="43"/>
       <c r="D319" s="6"/>
       <c r="F319" s="6"/>
       <c r="G319" s="6"/>
       <c r="H319" s="6"/>
     </row>
     <row r="320" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C320" s="44"/>
+      <c r="C320" s="43"/>
       <c r="D320" s="6"/>
       <c r="F320" s="6"/>
       <c r="G320" s="6"/>
       <c r="H320" s="6"/>
     </row>
     <row r="321" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C321" s="44"/>
+      <c r="C321" s="43"/>
       <c r="D321" s="6"/>
       <c r="F321" s="6"/>
       <c r="G321" s="6"/>
       <c r="H321" s="6"/>
     </row>
     <row r="322" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C322" s="44"/>
+      <c r="C322" s="43"/>
       <c r="D322" s="6"/>
       <c r="F322" s="6"/>
       <c r="G322" s="6"/>
       <c r="H322" s="6"/>
     </row>
     <row r="323" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C323" s="44"/>
+      <c r="C323" s="43"/>
       <c r="D323" s="6"/>
       <c r="F323" s="6"/>
       <c r="G323" s="6"/>
       <c r="H323" s="6"/>
     </row>
     <row r="324" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C324" s="44"/>
+      <c r="C324" s="43"/>
       <c r="D324" s="6"/>
       <c r="F324" s="6"/>
       <c r="G324" s="6"/>
       <c r="H324" s="6"/>
     </row>
     <row r="325" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C325" s="44"/>
+      <c r="C325" s="43"/>
       <c r="D325" s="6"/>
       <c r="F325" s="6"/>
       <c r="G325" s="6"/>
       <c r="H325" s="6"/>
     </row>
     <row r="326" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C326" s="44"/>
+      <c r="C326" s="43"/>
       <c r="D326" s="6"/>
       <c r="F326" s="6"/>
       <c r="G326" s="6"/>
       <c r="H326" s="6"/>
     </row>
     <row r="327" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C327" s="44"/>
+      <c r="C327" s="43"/>
       <c r="D327" s="6"/>
       <c r="F327" s="6"/>
       <c r="G327" s="6"/>
       <c r="H327" s="6"/>
     </row>
     <row r="328" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C328" s="44"/>
+      <c r="C328" s="43"/>
       <c r="D328" s="6"/>
       <c r="F328" s="6"/>
       <c r="G328" s="6"/>
       <c r="H328" s="6"/>
     </row>
     <row r="329" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C329" s="44"/>
+      <c r="C329" s="43"/>
       <c r="D329" s="6"/>
       <c r="F329" s="6"/>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
     </row>
     <row r="330" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C330" s="44"/>
+      <c r="C330" s="43"/>
       <c r="D330" s="6"/>
       <c r="F330" s="6"/>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
     </row>
     <row r="331" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C331" s="44"/>
+      <c r="C331" s="43"/>
       <c r="D331" s="6"/>
       <c r="F331" s="6"/>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
     </row>
     <row r="332" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C332" s="44"/>
+      <c r="C332" s="43"/>
       <c r="D332" s="6"/>
       <c r="F332" s="6"/>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
     </row>
     <row r="333" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C333" s="44"/>
+      <c r="C333" s="43"/>
       <c r="D333" s="6"/>
       <c r="F333" s="6"/>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
     </row>
     <row r="334" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C334" s="44"/>
+      <c r="C334" s="43"/>
       <c r="D334" s="6"/>
       <c r="F334" s="6"/>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
     </row>
     <row r="335" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C335" s="44"/>
+      <c r="C335" s="43"/>
       <c r="D335" s="6"/>
       <c r="F335" s="6"/>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
     </row>
     <row r="336" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C336" s="44"/>
+      <c r="C336" s="43"/>
       <c r="D336" s="6"/>
       <c r="F336" s="6"/>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
     </row>
     <row r="337" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C337" s="44"/>
+      <c r="C337" s="43"/>
       <c r="D337" s="6"/>
       <c r="F337" s="6"/>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
     </row>
     <row r="338" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C338" s="44"/>
+      <c r="C338" s="43"/>
       <c r="D338" s="6"/>
       <c r="F338" s="6"/>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
     </row>
     <row r="339" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C339" s="44"/>
+      <c r="C339" s="43"/>
       <c r="D339" s="6"/>
       <c r="F339" s="6"/>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
     </row>
     <row r="340" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C340" s="44"/>
+      <c r="C340" s="43"/>
       <c r="D340" s="6"/>
       <c r="F340" s="6"/>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
     </row>
     <row r="341" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C341" s="44"/>
+      <c r="C341" s="43"/>
       <c r="D341" s="6"/>
       <c r="F341" s="6"/>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
     </row>
     <row r="342" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C342" s="44"/>
+      <c r="C342" s="43"/>
       <c r="D342" s="6"/>
       <c r="F342" s="6"/>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
     </row>
     <row r="343" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C343" s="44"/>
+      <c r="C343" s="43"/>
       <c r="D343" s="6"/>
       <c r="F343" s="6"/>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
     </row>
     <row r="344" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C344" s="44"/>
+      <c r="C344" s="43"/>
       <c r="D344" s="6"/>
       <c r="F344" s="6"/>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
     </row>
     <row r="345" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C345" s="44"/>
+      <c r="C345" s="43"/>
       <c r="D345" s="6"/>
       <c r="F345" s="6"/>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
     </row>
     <row r="346" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C346" s="44"/>
+      <c r="C346" s="43"/>
       <c r="D346" s="6"/>
       <c r="F346" s="6"/>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
     </row>
     <row r="347" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C347" s="44"/>
+      <c r="C347" s="43"/>
       <c r="D347" s="6"/>
       <c r="F347" s="6"/>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
     </row>
     <row r="348" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C348" s="44"/>
+      <c r="C348" s="43"/>
       <c r="D348" s="6"/>
       <c r="F348" s="6"/>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
     </row>
     <row r="349" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C349" s="44"/>
+      <c r="C349" s="43"/>
       <c r="D349" s="6"/>
       <c r="F349" s="6"/>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
     </row>
     <row r="350" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C350" s="44"/>
+      <c r="C350" s="43"/>
       <c r="D350" s="6"/>
       <c r="F350" s="6"/>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
     </row>
     <row r="351" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C351" s="44"/>
+      <c r="C351" s="43"/>
       <c r="D351" s="6"/>
       <c r="F351" s="6"/>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
     </row>
     <row r="352" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C352" s="44"/>
+      <c r="C352" s="43"/>
       <c r="D352" s="6"/>
       <c r="F352" s="6"/>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
     </row>
     <row r="353" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C353" s="44"/>
+      <c r="C353" s="43"/>
       <c r="D353" s="6"/>
       <c r="F353" s="6"/>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
     </row>
     <row r="354" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C354" s="44"/>
+      <c r="C354" s="43"/>
       <c r="D354" s="6"/>
       <c r="F354" s="6"/>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
     </row>
     <row r="355" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C355" s="44"/>
+      <c r="C355" s="43"/>
       <c r="D355" s="6"/>
       <c r="F355" s="6"/>
       <c r="G355" s="6"/>
       <c r="H355" s="6"/>
     </row>
     <row r="356" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C356" s="44"/>
+      <c r="C356" s="43"/>
       <c r="D356" s="6"/>
       <c r="F356" s="6"/>
       <c r="G356" s="6"/>
       <c r="H356" s="6"/>
     </row>
     <row r="357" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C357" s="44"/>
+      <c r="C357" s="43"/>
       <c r="D357" s="6"/>
       <c r="F357" s="6"/>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
     </row>
     <row r="358" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C358" s="44"/>
+      <c r="C358" s="43"/>
       <c r="D358" s="6"/>
       <c r="F358" s="6"/>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
     </row>
     <row r="359" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C359" s="44"/>
+      <c r="C359" s="43"/>
       <c r="D359" s="6"/>
       <c r="F359" s="6"/>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
     </row>
     <row r="360" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C360" s="44"/>
+      <c r="C360" s="43"/>
       <c r="D360" s="6"/>
       <c r="F360" s="6"/>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
     </row>
     <row r="361" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C361" s="44"/>
+      <c r="C361" s="43"/>
       <c r="D361" s="6"/>
       <c r="F361" s="6"/>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
     </row>
     <row r="362" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C362" s="44"/>
+      <c r="C362" s="43"/>
       <c r="D362" s="6"/>
       <c r="F362" s="6"/>
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
     </row>
     <row r="363" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C363" s="44"/>
+      <c r="C363" s="43"/>
       <c r="D363" s="6"/>
       <c r="F363" s="6"/>
       <c r="G363" s="6"/>
       <c r="H363" s="6"/>
     </row>
     <row r="364" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C364" s="44"/>
+      <c r="C364" s="43"/>
       <c r="D364" s="6"/>
       <c r="F364" s="6"/>
       <c r="G364" s="6"/>
       <c r="H364" s="6"/>
     </row>
     <row r="365" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C365" s="44"/>
+      <c r="C365" s="43"/>
       <c r="D365" s="6"/>
       <c r="F365" s="6"/>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
     </row>
     <row r="366" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C366" s="44"/>
+      <c r="C366" s="43"/>
       <c r="D366" s="6"/>
       <c r="F366" s="6"/>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
     </row>
     <row r="367" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C367" s="44"/>
+      <c r="C367" s="43"/>
       <c r="D367" s="6"/>
       <c r="F367" s="6"/>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
     </row>
     <row r="368" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C368" s="44"/>
+      <c r="C368" s="43"/>
       <c r="D368" s="6"/>
       <c r="F368" s="6"/>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
     </row>
     <row r="369" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C369" s="44"/>
+      <c r="C369" s="43"/>
       <c r="D369" s="6"/>
       <c r="F369" s="6"/>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
     </row>
     <row r="370" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C370" s="44"/>
+      <c r="C370" s="43"/>
       <c r="D370" s="6"/>
       <c r="F370" s="6"/>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
     </row>
     <row r="371" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C371" s="44"/>
+      <c r="C371" s="43"/>
       <c r="D371" s="6"/>
       <c r="F371" s="6"/>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
     </row>
     <row r="372" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C372" s="44"/>
+      <c r="C372" s="43"/>
       <c r="D372" s="6"/>
       <c r="F372" s="6"/>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
     </row>
     <row r="373" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C373" s="44"/>
+      <c r="C373" s="43"/>
       <c r="D373" s="6"/>
       <c r="F373" s="6"/>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
     </row>
     <row r="374" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C374" s="44"/>
+      <c r="C374" s="43"/>
       <c r="D374" s="6"/>
       <c r="F374" s="6"/>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
     </row>
     <row r="375" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C375" s="44"/>
+      <c r="C375" s="43"/>
       <c r="D375" s="6"/>
       <c r="F375" s="6"/>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
     </row>
     <row r="376" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C376" s="44"/>
+      <c r="C376" s="43"/>
       <c r="D376" s="6"/>
       <c r="F376" s="6"/>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
     </row>
     <row r="377" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C377" s="44"/>
+      <c r="C377" s="43"/>
       <c r="D377" s="6"/>
       <c r="F377" s="6"/>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
     </row>
     <row r="378" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C378" s="44"/>
+      <c r="C378" s="43"/>
       <c r="D378" s="6"/>
       <c r="F378" s="6"/>
       <c r="G378" s="6"/>
       <c r="H378" s="6"/>
     </row>
     <row r="379" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C379" s="44"/>
+      <c r="C379" s="43"/>
       <c r="D379" s="6"/>
       <c r="F379" s="6"/>
       <c r="G379" s="6"/>
       <c r="H379" s="6"/>
     </row>
     <row r="380" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C380" s="44"/>
+      <c r="C380" s="43"/>
       <c r="D380" s="6"/>
       <c r="F380" s="6"/>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
     </row>
     <row r="381" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C381" s="44"/>
+      <c r="C381" s="43"/>
       <c r="D381" s="6"/>
       <c r="F381" s="6"/>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
     </row>
     <row r="382" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C382" s="44"/>
+      <c r="C382" s="43"/>
       <c r="D382" s="6"/>
       <c r="F382" s="6"/>
       <c r="G382" s="6"/>
       <c r="H382" s="6"/>
     </row>
     <row r="383" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C383" s="44"/>
+      <c r="C383" s="43"/>
       <c r="D383" s="6"/>
       <c r="F383" s="6"/>
       <c r="G383" s="6"/>
       <c r="H383" s="6"/>
     </row>
     <row r="384" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C384" s="44"/>
+      <c r="C384" s="43"/>
       <c r="D384" s="6"/>
       <c r="F384" s="6"/>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
     </row>
     <row r="385" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C385" s="44"/>
+      <c r="C385" s="43"/>
       <c r="D385" s="6"/>
       <c r="F385" s="6"/>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
     </row>
     <row r="386" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C386" s="44"/>
+      <c r="C386" s="43"/>
       <c r="D386" s="6"/>
       <c r="F386" s="6"/>
       <c r="G386" s="6"/>
       <c r="H386" s="6"/>
     </row>
     <row r="387" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C387" s="44"/>
+      <c r="C387" s="43"/>
       <c r="D387" s="6"/>
       <c r="F387" s="6"/>
       <c r="G387" s="6"/>
       <c r="H387" s="6"/>
     </row>
     <row r="388" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C388" s="44"/>
+      <c r="C388" s="43"/>
       <c r="D388" s="6"/>
       <c r="F388" s="6"/>
       <c r="G388" s="6"/>
       <c r="H388" s="6"/>
     </row>
     <row r="389" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C389" s="44"/>
+      <c r="C389" s="43"/>
       <c r="D389" s="6"/>
       <c r="F389" s="6"/>
       <c r="G389" s="6"/>
       <c r="H389" s="6"/>
     </row>
     <row r="390" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C390" s="44"/>
+      <c r="C390" s="43"/>
       <c r="D390" s="6"/>
       <c r="F390" s="6"/>
       <c r="G390" s="6"/>
       <c r="H390" s="6"/>
     </row>
     <row r="391" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C391" s="44"/>
+      <c r="C391" s="43"/>
       <c r="D391" s="6"/>
       <c r="F391" s="6"/>
       <c r="G391" s="6"/>
       <c r="H391" s="6"/>
     </row>
     <row r="392" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C392" s="44"/>
+      <c r="C392" s="43"/>
       <c r="D392" s="6"/>
       <c r="F392" s="6"/>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
     </row>
     <row r="393" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C393" s="44"/>
+      <c r="C393" s="43"/>
       <c r="D393" s="6"/>
       <c r="F393" s="6"/>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
     </row>
     <row r="394" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C394" s="44"/>
+      <c r="C394" s="43"/>
       <c r="D394" s="6"/>
       <c r="F394" s="6"/>
       <c r="G394" s="6"/>
       <c r="H394" s="6"/>
     </row>
     <row r="395" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C395" s="44"/>
+      <c r="C395" s="43"/>
       <c r="D395" s="6"/>
       <c r="F395" s="6"/>
       <c r="G395" s="6"/>
       <c r="H395" s="6"/>
     </row>
     <row r="396" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C396" s="44"/>
+      <c r="C396" s="43"/>
       <c r="D396" s="6"/>
       <c r="F396" s="6"/>
       <c r="G396" s="6"/>
       <c r="H396" s="6"/>
     </row>
     <row r="397" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C397" s="44"/>
+      <c r="C397" s="43"/>
       <c r="D397" s="6"/>
       <c r="F397" s="6"/>
       <c r="G397" s="6"/>
       <c r="H397" s="6"/>
     </row>
+    <row r="398" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C398" s="43"/>
+      <c r="D398" s="6"/>
+      <c r="F398" s="6"/>
+      <c r="G398" s="6"/>
+      <c r="H398" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="A5:H9"/>
+  <mergeCells count="6">
+    <mergeCell ref="A3:H5"/>
+    <mergeCell ref="A6:H10"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E11:H397">
+  <conditionalFormatting sqref="E12:H398">
     <cfRule type="expression" dxfId="0" priority="23">
-      <formula>AND(NOT(ISBLANK($D11)),ISBLANK(E11))</formula>
+      <formula>AND(NOT(ISBLANK($D12)),ISBLANK(E12))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -7388,6 +7542,7 @@
   <headerFooter>
     <oddHeader>&amp;R&amp;"Aptos"&amp;12&amp;K000000 Unclassified / Non classifié&amp;1#_x000D_</oddHeader>
   </headerFooter>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7413,51 +7568,51 @@
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="123"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="124"/>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="125"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="128"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
@@ -7555,8 +7710,8 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -7565,8 +7720,8 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -7575,8 +7730,8 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -7585,8 +7740,8 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -7595,8 +7750,8 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -7605,8 +7760,8 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -7615,8 +7770,8 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -7625,8 +7780,8 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -7635,8 +7790,8 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -7645,8 +7800,8 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -7655,8 +7810,8 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -7665,8 +7820,8 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -7675,8 +7830,8 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -7685,8 +7840,8 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -7695,8 +7850,8 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -7705,8 +7860,8 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -7715,8 +7870,8 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
@@ -7725,8 +7880,8 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
@@ -7735,8 +7890,8 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
@@ -7745,8 +7900,8 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
@@ -7755,8 +7910,8 @@
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
@@ -7765,8 +7920,8 @@
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
@@ -7775,8 +7930,8 @@
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
@@ -7829,63 +7984,63 @@
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="84"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="87"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="63"/>
     </row>
     <row r="6" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
@@ -7983,8 +8138,8 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -7993,8 +8148,8 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -8003,8 +8158,8 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -8013,8 +8168,8 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -8023,8 +8178,8 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -8033,8 +8188,8 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -8043,8 +8198,8 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -8053,8 +8208,8 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -8063,8 +8218,8 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -8073,8 +8228,8 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -8083,8 +8238,8 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -8093,8 +8248,8 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -8103,8 +8258,8 @@
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -8113,8 +8268,8 @@
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -8123,8 +8278,8 @@
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -8133,8 +8288,8 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
@@ -8143,8 +8298,8 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
@@ -8153,8 +8308,8 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
@@ -8163,8 +8318,8 @@
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
@@ -8173,8 +8328,8 @@
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
@@ -8183,8 +8338,8 @@
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
@@ -8193,8 +8348,8 @@
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
@@ -8203,8 +8358,8 @@
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
@@ -8521,7 +8676,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:H34 F38:H1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:H1048576 F7:H34" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8557,75 +8712,75 @@
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="132"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="134"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="133"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="134"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="134"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="133"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="134"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
@@ -8723,8 +8878,8 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -8733,8 +8888,8 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -8743,8 +8898,8 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -8753,8 +8908,8 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -8763,8 +8918,8 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -8773,8 +8928,8 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -8783,8 +8938,8 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -8793,8 +8948,8 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -8803,8 +8958,8 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -8813,8 +8968,8 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -8823,8 +8978,8 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -9326,7 +9481,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:H1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:H1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9361,75 +9516,75 @@
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="84"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="83"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="84"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="87"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
@@ -9527,8 +9682,8 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -9537,8 +9692,8 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -9547,8 +9702,8 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -9557,8 +9712,8 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -9567,8 +9722,8 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -9577,8 +9732,8 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -9587,8 +9742,8 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -9597,8 +9752,8 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -9607,8 +9762,8 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -9617,8 +9772,8 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -9627,8 +9782,8 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -10230,7 +10385,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:H1048576" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:H1048576" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10266,93 +10421,93 @@
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
+      <c r="A2" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="83"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="83"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
     </row>
     <row r="8" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
@@ -11431,7 +11586,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:H9 F11:H1048576" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:H9 F12:H1048576" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11466,80 +11621,80 @@
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="91"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="109"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="94"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="112"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="94"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="94"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="112"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="95"/>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="97"/>
+      <c r="A6" s="113"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="115"/>
     </row>
     <row r="7" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
@@ -11706,7 +11861,7 @@
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="44"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -11719,7 +11874,7 @@
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="44"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -11732,7 +11887,7 @@
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
-      <c r="C19" s="44"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -11745,7 +11900,7 @@
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
-      <c r="C20" s="44"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -11758,7 +11913,7 @@
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
-      <c r="C21" s="44"/>
+      <c r="C21" s="43"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
@@ -11771,7 +11926,7 @@
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
-      <c r="C22" s="44"/>
+      <c r="C22" s="43"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -11784,7 +11939,7 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
-      <c r="C23" s="44"/>
+      <c r="C23" s="43"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -11797,7 +11952,7 @@
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
-      <c r="C24" s="44"/>
+      <c r="C24" s="43"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -11810,7 +11965,7 @@
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
-      <c r="C25" s="44"/>
+      <c r="C25" s="43"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -11823,7 +11978,7 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
-      <c r="C26" s="44"/>
+      <c r="C26" s="43"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -11836,7 +11991,7 @@
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
-      <c r="C27" s="44"/>
+      <c r="C27" s="43"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -11849,7 +12004,7 @@
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
-      <c r="C28" s="44"/>
+      <c r="C28" s="43"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -11862,7 +12017,7 @@
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="44"/>
+      <c r="C29" s="43"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -11875,7 +12030,7 @@
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="44"/>
+      <c r="C30" s="43"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -11888,7 +12043,7 @@
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="44"/>
+      <c r="C31" s="43"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -11901,7 +12056,7 @@
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="17"/>
-      <c r="C32" s="44"/>
+      <c r="C32" s="43"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -11914,7 +12069,7 @@
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="17"/>
-      <c r="C33" s="44"/>
+      <c r="C33" s="43"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -11927,7 +12082,7 @@
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="17"/>
-      <c r="C34" s="44"/>
+      <c r="C34" s="43"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -11940,7 +12095,7 @@
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="17"/>
-      <c r="C35" s="44"/>
+      <c r="C35" s="43"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -11953,7 +12108,7 @@
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="17"/>
-      <c r="C36" s="44"/>
+      <c r="C36" s="43"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -11966,7 +12121,7 @@
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
-      <c r="C37" s="44"/>
+      <c r="C37" s="43"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -11979,7 +12134,7 @@
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="17"/>
-      <c r="C38" s="44"/>
+      <c r="C38" s="43"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -11992,7 +12147,7 @@
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="17"/>
-      <c r="C39" s="44"/>
+      <c r="C39" s="43"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -12005,7 +12160,7 @@
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="17"/>
-      <c r="C40" s="44"/>
+      <c r="C40" s="43"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -12018,7 +12173,7 @@
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="17"/>
-      <c r="C41" s="44"/>
+      <c r="C41" s="43"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -12031,7 +12186,7 @@
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="17"/>
-      <c r="C42" s="44"/>
+      <c r="C42" s="43"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -12044,7 +12199,7 @@
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="17"/>
-      <c r="C43" s="44"/>
+      <c r="C43" s="43"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -12057,7 +12212,7 @@
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="17"/>
-      <c r="C44" s="44"/>
+      <c r="C44" s="43"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -12070,7 +12225,7 @@
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="17"/>
-      <c r="C45" s="44"/>
+      <c r="C45" s="43"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -12083,7 +12238,7 @@
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="17"/>
-      <c r="C46" s="44"/>
+      <c r="C46" s="43"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -12096,7 +12251,7 @@
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
-      <c r="C47" s="44"/>
+      <c r="C47" s="43"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
@@ -12109,7 +12264,7 @@
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="17"/>
-      <c r="C48" s="44"/>
+      <c r="C48" s="43"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
@@ -12122,7 +12277,7 @@
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
-      <c r="C49" s="44"/>
+      <c r="C49" s="43"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -12135,7 +12290,7 @@
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="17"/>
       <c r="B50" s="17"/>
-      <c r="C50" s="44"/>
+      <c r="C50" s="43"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -12148,7 +12303,7 @@
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="17"/>
-      <c r="C51" s="44"/>
+      <c r="C51" s="43"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
@@ -12161,7 +12316,7 @@
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="17"/>
       <c r="B52" s="17"/>
-      <c r="C52" s="44"/>
+      <c r="C52" s="43"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
@@ -12174,7 +12329,7 @@
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="17"/>
       <c r="B53" s="17"/>
-      <c r="C53" s="44"/>
+      <c r="C53" s="43"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
@@ -12187,7 +12342,7 @@
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="17"/>
       <c r="B54" s="17"/>
-      <c r="C54" s="44"/>
+      <c r="C54" s="43"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
@@ -12200,7 +12355,7 @@
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="17"/>
-      <c r="C55" s="44"/>
+      <c r="C55" s="43"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
@@ -12213,7 +12368,7 @@
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
-      <c r="C56" s="44"/>
+      <c r="C56" s="43"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
@@ -12226,7 +12381,7 @@
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="17"/>
-      <c r="C57" s="44"/>
+      <c r="C57" s="43"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
@@ -12239,7 +12394,7 @@
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="17"/>
       <c r="B58" s="17"/>
-      <c r="C58" s="44"/>
+      <c r="C58" s="43"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
@@ -12252,7 +12407,7 @@
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
       <c r="B59" s="17"/>
-      <c r="C59" s="44"/>
+      <c r="C59" s="43"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -12265,7 +12420,7 @@
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="17"/>
       <c r="B60" s="17"/>
-      <c r="C60" s="44"/>
+      <c r="C60" s="43"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -12278,7 +12433,7 @@
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
       <c r="B61" s="17"/>
-      <c r="C61" s="44"/>
+      <c r="C61" s="43"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -12291,7 +12446,7 @@
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="17"/>
-      <c r="C62" s="44"/>
+      <c r="C62" s="43"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -12304,7 +12459,7 @@
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="17"/>
       <c r="B63" s="17"/>
-      <c r="C63" s="44"/>
+      <c r="C63" s="43"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -12317,7 +12472,7 @@
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="17"/>
-      <c r="C64" s="44"/>
+      <c r="C64" s="43"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -12330,7 +12485,7 @@
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="17"/>
       <c r="B65" s="17"/>
-      <c r="C65" s="44"/>
+      <c r="C65" s="43"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -12343,7 +12498,7 @@
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="17"/>
-      <c r="C66" s="44"/>
+      <c r="C66" s="43"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -12356,7 +12511,7 @@
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="17"/>
-      <c r="C67" s="44"/>
+      <c r="C67" s="43"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -12369,7 +12524,7 @@
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="17"/>
-      <c r="C68" s="44"/>
+      <c r="C68" s="43"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -12382,7 +12537,7 @@
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="17"/>
       <c r="B69" s="17"/>
-      <c r="C69" s="44"/>
+      <c r="C69" s="43"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -12395,7 +12550,7 @@
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="17"/>
       <c r="B70" s="17"/>
-      <c r="C70" s="44"/>
+      <c r="C70" s="43"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -12408,7 +12563,7 @@
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="17"/>
       <c r="B71" s="17"/>
-      <c r="C71" s="44"/>
+      <c r="C71" s="43"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -12421,7 +12576,7 @@
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="17"/>
       <c r="B72" s="17"/>
-      <c r="C72" s="44"/>
+      <c r="C72" s="43"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -12434,7 +12589,7 @@
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="17"/>
       <c r="B73" s="17"/>
-      <c r="C73" s="44"/>
+      <c r="C73" s="43"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -12447,7 +12602,7 @@
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="17"/>
-      <c r="C74" s="44"/>
+      <c r="C74" s="43"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -12460,7 +12615,7 @@
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="17"/>
       <c r="B75" s="17"/>
-      <c r="C75" s="44"/>
+      <c r="C75" s="43"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -12473,7 +12628,7 @@
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="17"/>
       <c r="B76" s="17"/>
-      <c r="C76" s="44"/>
+      <c r="C76" s="43"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -12520,7 +12675,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:H8 F10:H1048576" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:H8 F11:H1048576" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12552,65 +12707,65 @@
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="41"/>
+      <c r="D1" s="42" t="s">
         <v>53</v>
       </c>
       <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="84"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="83"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="60"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="84"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="84"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="63"/>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="98" t="s">
+      <c r="A8" s="116" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="98" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
+      <c r="A9" s="117"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="117"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
+      <c r="A10" s="45"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
     </row>
@@ -12655,87 +12810,87 @@
       <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="45"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="45"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="45"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="45"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
+      <c r="A30" s="44"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
+      <c r="A31" s="44"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="45"/>
+      <c r="A32" s="44"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="45"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="45"/>
+      <c r="A34" s="44"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="45"/>
+      <c r="A35" s="44"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
     </row>
@@ -12765,7 +12920,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="17" customWidth="1"/>
@@ -12781,95 +12936,95 @@
     <col min="11" max="11" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="78"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="39" t="s">
+      <c r="C1" s="54"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="38"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="61"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
+    </row>
+    <row r="5" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="132"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="135"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="137"/>
-    </row>
-    <row r="4" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="E5" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
@@ -12963,443 +13118,456 @@
       <c r="K12" s="29"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C14" s="44"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="44"/>
+      <c r="C15" s="43"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C16" s="44"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="44"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="44"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="44"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="44"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="44"/>
+      <c r="C21" s="43"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="44"/>
+      <c r="C22" s="43"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="44"/>
+      <c r="C23" s="43"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="44"/>
+      <c r="C24" s="43"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="44"/>
+      <c r="C25" s="43"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="44"/>
+      <c r="C26" s="43"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="44"/>
+      <c r="C27" s="43"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="44"/>
+      <c r="C28" s="43"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C29" s="44"/>
+      <c r="C29" s="43"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="44"/>
+      <c r="C30" s="43"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="44"/>
+      <c r="C31" s="43"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C32" s="44"/>
+      <c r="C32" s="43"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="44"/>
+      <c r="C33" s="43"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="44"/>
+      <c r="C34" s="43"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="44"/>
+      <c r="C35" s="43"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C36" s="44"/>
+      <c r="C36" s="43"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
-      <c r="J36" s="47"/>
-      <c r="K36" s="47"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C37" s="44"/>
+      <c r="C37" s="43"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="47"/>
-      <c r="K37" s="47"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="46"/>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="44"/>
+      <c r="C38" s="43"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="44"/>
+      <c r="C39" s="43"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
     </row>
     <row r="40" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C40" s="44"/>
+      <c r="C40" s="43"/>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="47"/>
-      <c r="K40" s="47"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="46"/>
     </row>
     <row r="41" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C41" s="44"/>
+      <c r="C41" s="43"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
     </row>
     <row r="42" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C42" s="44"/>
+      <c r="C42" s="43"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C43" s="44"/>
+      <c r="C43" s="43"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
     </row>
     <row r="44" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C44" s="44"/>
+      <c r="C44" s="43"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
     </row>
     <row r="45" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C45" s="44"/>
+      <c r="C45" s="43"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
     </row>
     <row r="46" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C46" s="44"/>
+      <c r="C46" s="43"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C47" s="44"/>
+      <c r="C47" s="43"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="46"/>
     </row>
     <row r="48" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C48" s="44"/>
+      <c r="C48" s="43"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
-      <c r="J48" s="47"/>
-      <c r="K48" s="47"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
     </row>
     <row r="49" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="44"/>
+      <c r="C49" s="43"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
     </row>
     <row r="50" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="44"/>
+      <c r="C50" s="43"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="46"/>
+    </row>
+    <row r="51" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C51" s="43"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="46"/>
+      <c r="K51" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K3"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A2:K4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="D4:E4">
+  <conditionalFormatting sqref="D5:E5">
     <cfRule type="expression" dxfId="3" priority="21">
-      <formula>AND(NOT(ISBLANK($A17)),ISBLANK(D4))</formula>
+      <formula>AND(NOT(ISBLANK($A18)),ISBLANK(D5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:K50">
+  <conditionalFormatting sqref="E6:K51">
     <cfRule type="expression" dxfId="2" priority="19">
-      <formula>AND(NOT(ISBLANK($D5)),ISBLANK(E5))</formula>
+      <formula>AND(NOT(ISBLANK($D6)),ISBLANK(E6))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:I1048576" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I1048576" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
